--- a/01_analyses_mask-ONEland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-ONEland/results/SoIB_summaries.xlsx
@@ -399,10 +399,10 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="E2">
-        <v>20.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>22.2</v>
       </c>
       <c r="E3">
-        <v>41.7</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="4">
@@ -431,13 +431,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>11.1</v>
       </c>
       <c r="E4">
         <v>33.3</v>
@@ -453,13 +453,13 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>69</v>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>49</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2">
-        <v>84.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -795,16 +795,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>12.6</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1.1</v>
+        <v>11.7</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_mask-ONEland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-ONEland/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="E2">
-        <v>15.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>22.2</v>
       </c>
       <c r="E3">
-        <v>36.8</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>11.1</v>
       </c>
       <c r="E4">
-        <v>42.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="5">
@@ -456,10 +456,10 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E5">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>69</v>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +706,7 @@
         <v>49</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2">
-        <v>83.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2">
-        <v>97.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -795,16 +795,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>13.6</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2.3</v>
+        <v>11.7</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_mask-ONEland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-ONEland/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>55.6</v>
+        <v>45.8</v>
       </c>
       <c r="E2">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>22.2</v>
+        <v>33.3</v>
       </c>
       <c r="E3">
-        <v>44.4</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E4">
-        <v>33.3</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="5">
@@ -453,13 +453,13 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>11.1</v>
+        <v>4.2</v>
       </c>
       <c r="E5">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2">
-        <v>85.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="D2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -782,10 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>2.9</v>
+        <v>4.9</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -799,6 +805,12 @@
       </c>
       <c r="C4">
         <v>11.7</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
